--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/todos.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/todos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="endoprotesis-ortoped todos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="endoprotesis-ortoped todos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/todos.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/todos.xlsx
@@ -745,7 +745,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +993,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1058,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +1977,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2042,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2717,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3087,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3152,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3400,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3892,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5360,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5486,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5612,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +5921,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6108,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6356,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6482,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +7950,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8259,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +8995,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9365,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9430,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +10959,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11024,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11577,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +11947,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12439,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +12809,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +12874,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13000,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13065,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +14594,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15086,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15395,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16192,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16318,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16444,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +16631,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +16940,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17005,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +17863,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +17989,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18115,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +18790,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +19465,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +20445,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +20632,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +20941,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21006,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +21742,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22173,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +23519,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +23828,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +23893,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24019,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +24145,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +24332,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +24397,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +24523,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +24588,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +24714,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +25084,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +25149,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +25214,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +25279,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +26625,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +26812,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +26938,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +27003,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +27251,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +28170,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +28418,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +28483,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +28731,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +28979,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +29044,11 @@
           <t>77.447.444-7</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
